--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_07_Data Foundations, Embedding _ Vector Store/Day_07_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_07_Data Foundations, Embedding _ Vector Store/Day_07_Phan_01_21_Cau.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1145,7 +1145,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Sau bốn chunk đầy đủ vẫn còn 50 ký tự cần được phủ.</t>
+          <t>Với văn bản dài 1050 ký tự, chunk_size=250 và overlap=0 (step = 250): các chunk bắt đầu tại 0, 250, 500, 750 (4 chunk đầy đủ 250 ký tự = 1000 ký tự) và chunk thứ 5 bắt đầu tại vị trí 1000 chứa 50 ký tự còn lại. Do đó tạo ra 5 chunk, chunk cuối cùng có 50 ký tự.</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1462,7 +1462,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mục tiêu là trả truy vấn đúng, không tối thiểu hóa số lượng chunk.</t>
+          <t>Số lượng chunk ít không đồng nghĩa với chất lượng truy xuất cao. Nếu một chiến lược chia chunk bỏ sót toàn bộ các truy vấn về ngoại lệ, cần thay đổi hoặc kết hợp chiến lược chia chunk (ví dụ phân cấp hoặc theo ranh giới cấu trúc) để đảm bảo độ bao phủ bằng chứng.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o4 → o1 → o3</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Pooling chỉ xảy ra sau khi đã có token representations.</t>
+          <t>Quy trình kỹ thuật chuẩn để tạo vector embedding từ một đoạn văn bản: 1. Tokenize văn bản đầu vào (o2) -&gt; 2. Encoder tạo biểu diễn ngữ cảnh cho các token (o4) -&gt; 3. Áp dụng pooling (mean/CLS) để tổng hợp các token representations thành một vector (o1) -&gt; 4. Xuất ra và chuẩn hóa vector cuối cùng (o3).</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.447</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là tích hai độ lớn.</t>
+          <t>Độ tương đồng cosine: cos(θ) = (a · b) / (||a|| × ||b||). Với a = [1, 2] và b = [2, 0]: a · b = 1×2 + 2×0 = 2; ||a|| = √(1² + 2²) = √5 ≈ 2,23607; ||b|| = √(2² + 0²) = 2. Do đó cos(θ) = 2 / (√5 × 2) = 1 / √5 ≈ 0,4472136. Làm tròn ba chữ số thập phân là 0,447.</t>
         </is>
       </c>
     </row>
